--- a/bookkeeper-v2/v2-consulting/02-Practice-Dashboard/Bookkeeper-Practice-Dashboard-v2.xlsx
+++ b/bookkeeper-v2/v2-consulting/02-Practice-Dashboard/Bookkeeper-Practice-Dashboard-v2.xlsx
@@ -4,21 +4,33 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setup" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client CRM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lead Pipeline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Calculator" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Close" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Tracker" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Documents" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Planner" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navigation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setup" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client CRM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lead Pipeline" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Calculator" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Close" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Tracker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Documents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity Planner" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Setup'!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Client CRM'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Lead Pipeline'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Pricing Calculator'!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Monthly Close'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Invoice Tracker'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Tax Documents'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Capacity Planner'!$1:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Dashboard'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Instructions'!$1:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,13 +41,60 @@
     <numFmt numFmtId="164" formatCode="€#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0F766E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFD97706"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -51,26 +110,9 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF64748B"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF0F766E"/>
       <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF0F172A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF0F172A"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -82,12 +124,6 @@
       <name val="Calibri"/>
       <color rgb="FF0F172A"/>
       <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF0F766E"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -134,13 +170,13 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -178,6 +214,12 @@
       <color rgb="FF64748B"/>
       <sz val="7.5"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -185,6 +227,11 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -198,12 +245,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -216,11 +263,6 @@
         <fgColor rgb="FFD97706"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="20">
     <border>
@@ -231,6 +273,15 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF0F766E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0F766E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0F766E"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF0F766E"/>
       </bottom>
@@ -247,6 +298,25 @@
       </top>
       <bottom style="thin">
         <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD97706"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF0F766E"/>
       </bottom>
     </border>
     <border>
@@ -292,34 +362,6 @@
         <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD97706"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF0F766E"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF0F766E"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF0F766E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF0F766E"/>
-      </bottom>
     </border>
     <border>
       <left style="medium">
@@ -455,149 +497,194 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="16" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="23" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -645,6 +732,27 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8FAFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0010B981"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EF4444"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1011,6 +1119,1150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:T22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="6" customHeight="1"/>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>NOVAOPS  ·  Bookkeeper Practice Dashboard  ·  v2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Your complete practice operations system</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="3" customHeight="1">
+      <c r="A4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="14" customHeight="1"/>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>This landing page — start here</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Enter your practice name, pricing tiers, and settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Client CRM</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Master record for all active and former clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Lead Pipeline</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Track every prospect from first contact to closed deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Pricing Calculator</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Calculate client fees and cleanup estimates instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Monthly Close</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Track monthly close status and checklist for every client</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Invoice Tracker</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Log invoices, payment status, and outstanding balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tax Documents</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Year-end document collection tracker per client</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Capacity Planner</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Plan available hours vs. committed client time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Live KPI overview — auto-populates from all sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Full usage guide for every sheet in this system</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>HOW TO START</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Step 1: Go to Setup sheet and fill all amber cells.
+Step 2: Add your clients in Client CRM.
+Step 3: Use Dashboard to track everything at a glance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>© 2025 NovaOps  ·  Bookkeeper Practice Launch System  ·  Commercial Use License</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A22:T22"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A2:T2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F172A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:T25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14" customHeight="1"/>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>NOVAOPS  ·  BOOKKEEPER PRACTICE DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="52" t="inlineStr">
+        <is>
+          <t>v2.0   ·   Consulting Edition   ·   Live data from all sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="4" customHeight="1">
+      <c r="A4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="13" customHeight="1">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>ACTIVE CLIENTS</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>MONTHLY RECURRING REVENUE</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="19" t="n"/>
+      <c r="G6" s="53" t="inlineStr">
+        <is>
+          <t>OPEN PIPELINE VALUE</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="53" t="inlineStr">
+        <is>
+          <t>ACTIVE LEADS</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="19" t="n"/>
+      <c r="M6" s="53" t="inlineStr">
+        <is>
+          <t>TOTAL INVOICED (YTD)</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="53" t="inlineStr">
+        <is>
+          <t>CLOSES IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="54">
+        <f>COUNTIF('Client CRM'!C:C,"Active")</f>
+        <v/>
+      </c>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="55">
+        <f>SUMIF('Client CRM'!C:C,"Active",'Client CRM'!F:F)</f>
+        <v/>
+      </c>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="56">
+        <f>SUMIF('Lead Pipeline'!D:D,"&lt;&gt;Closed Lost",'Lead Pipeline'!F:F)</f>
+        <v/>
+      </c>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="57">
+        <f>COUNTIF('Lead Pipeline'!D:D,"&lt;&gt;Closed Lost")-COUNTIF('Lead Pipeline'!D:D,"Closed Won")</f>
+        <v/>
+      </c>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="55">
+        <f>SUMIF('Invoice Tracker'!G:G,"&lt;&gt;Void",'Invoice Tracker'!F:F)</f>
+        <v/>
+      </c>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="54">
+        <f>COUNTIF('Monthly Close'!D:D,"In Progress")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t>from Client CRM</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="58" t="inlineStr">
+        <is>
+          <t>total active fees</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="58" t="inlineStr">
+        <is>
+          <t>est. monthly from leads</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="58" t="inlineStr">
+        <is>
+          <t>in pipeline</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="19" t="n"/>
+      <c r="M8" s="58" t="inlineStr">
+        <is>
+          <t>all non-void invoices</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="58" t="inlineStr">
+        <is>
+          <t>this month</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="4" customHeight="1">
+      <c r="A9" s="59" t="n"/>
+      <c r="B9" s="59" t="n"/>
+      <c r="C9" s="59" t="n"/>
+      <c r="D9" s="59" t="n"/>
+      <c r="E9" s="59" t="n"/>
+      <c r="F9" s="59" t="n"/>
+      <c r="G9" s="60" t="n"/>
+      <c r="H9" s="60" t="n"/>
+      <c r="I9" s="60" t="n"/>
+      <c r="J9" s="60" t="n"/>
+      <c r="K9" s="60" t="n"/>
+      <c r="L9" s="60" t="n"/>
+      <c r="M9" s="59" t="n"/>
+      <c r="N9" s="59" t="n"/>
+      <c r="O9" s="59" t="n"/>
+      <c r="P9" s="59" t="n"/>
+      <c r="Q9" s="59" t="n"/>
+      <c r="R9" s="59" t="n"/>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>01 — ACTIVE CLIENT SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Fee (€)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>Close Day</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="22">
+        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="25">
+        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="22">
+        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>02 — MONTHLY CLOSE STATUS — CURRENT PERIOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Bank Rec</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Reports Delivered</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!C:C,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!D:D,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!F:F,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!J:J,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!K:K,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!E:E,1+1),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!C:C,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!D:D,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!F:F,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!J:J,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!K:K,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="25">
+        <f>IFERROR(INDEX('Monthly Close'!E:E,2+1),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!C:C,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!D:D,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!F:F,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!J:J,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!K:K,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="22">
+        <f>IFERROR(INDEX('Monthly Close'!E:E,3+1),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>Dashboard auto-updates when you open this file</t>
+        </is>
+      </c>
+      <c r="I25" s="63" t="inlineStr">
+        <is>
+          <t>LAST UPDATED</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="64">
+        <f>TEXT(NOW(),"MMMM D, YYYY")</f>
+        <v/>
+      </c>
+      <c r="M25" s="38" t="n"/>
+      <c r="N25" s="38" t="n"/>
+      <c r="O25" s="38" t="n"/>
+      <c r="P25" s="39" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="L25:P25"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="E21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:R29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.5" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="10" customHeight="1"/>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>— INSTRUCTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>How to use every sheet in this dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="3" customHeight="1">
+      <c r="A4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="8" customHeight="1"/>
+    <row r="6" ht="36" customHeight="1">
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>00 — NAVIGATION</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Branded landing page. Overview of all sheets and quick-start guide.</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="18" t="n"/>
+      <c r="P6" s="19" t="n"/>
+    </row>
+    <row r="7" ht="4" customHeight="1"/>
+    <row r="8" ht="36" customHeight="1">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>01 — SETUP</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="66" t="inlineStr">
+        <is>
+          <t>Fill in the amber cells only. White cells contain formulas that reference Setup data — do not edit them. Changes to Practice Name and pricing cascade to the Pricing Calculator.</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+      <c r="P8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="4" customHeight="1"/>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>02 — CLIENT CRM</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="66" t="inlineStr">
+        <is>
+          <t>Add one row per client. The Status column (Active/Churned/On Hold) drives the Dashboard KPIs. Use the Package dropdown to match your service tiers. The MRR formula at the bottom sums only Active clients.</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="18" t="n"/>
+      <c r="O10" s="18" t="n"/>
+      <c r="P10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="4" customHeight="1"/>
+    <row r="12" ht="36" customHeight="1">
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>03 — LEAD PIPELINE</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>Add a row for each prospect. The Pipeline Value at the bottom sums all leads not marked Closed Lost. Move Stage through the dropdown — from New Inquiry to Closed Won.</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
+      <c r="P12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="4" customHeight="1"/>
+    <row r="14" ht="36" customHeight="1">
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>04 — PRICING CALCULATOR</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="66" t="inlineStr">
+        <is>
+          <t>Enter the prospect's details in the amber cells. The calculator produces a recommended monthly fee and cleanup estimate. Use it during diagnostic calls.</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="18" t="n"/>
+      <c r="P14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="4" customHeight="1"/>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>05 — MONTHLY CLOSE</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="66" t="inlineStr">
+        <is>
+          <t>Add one row per client per period (e.g., "2026-07"). Use the Status and checkbox dropdowns (Yes/No) to track progress. The Close Progress row at the bottom shows your completion percentage.</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="4" customHeight="1"/>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>06 — INVOICE TRACKER</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="66" t="inlineStr">
+        <is>
+          <t>Add one row per invoice. Status drives the Outstanding balance formula at the bottom. Mark Paid invoices with the payment date. Overdue rows turn red automatically.</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="18" t="n"/>
+      <c r="P18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="4" customHeight="1"/>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>07 — TAX DOCUMENTS</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="66" t="inlineStr">
+        <is>
+          <t>Use this sheet at year-end. One row per client per fiscal year. Track document collection across all categories. Mark items N/A if they do not apply to that client.</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="18" t="n"/>
+      <c r="P20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="4" customHeight="1"/>
+    <row r="22" ht="36" customHeight="1">
+      <c r="B22" s="65" t="inlineStr">
+        <is>
+          <t>08 — CAPACITY PLANNER</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="66" t="inlineStr">
+        <is>
+          <t>Enter your weekly available hours and admin time. Add one row per client with their average monthly hours. The sheet shows whether you are over or under capacity.</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="18" t="n"/>
+      <c r="P22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="4" customHeight="1"/>
+    <row r="24" ht="36" customHeight="1">
+      <c r="B24" s="65" t="inlineStr">
+        <is>
+          <t>09 — DASHBOARD</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="66" t="inlineStr">
+        <is>
+          <t>This sheet auto-populates from all other sheets. Do not enter data here directly. KPI cards show active clients, MRR, pipeline value, and close status in real time. Last Updated shows today's date.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+      <c r="P24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="4" customHeight="1"/>
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="65" t="inlineStr">
+        <is>
+          <t>10 — INSTRUCTIONS</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="66" t="inlineStr">
+        <is>
+          <t>This sheet. Reference it anytime you are unsure about a feature.</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="18" t="n"/>
+      <c r="P26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="4" customHeight="1"/>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>TIP: Only edit cells with amber background. Never edit cells with teal or dark backgrounds — those contain formulas or are read-only display areas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="E20:P20"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E10:P10"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B29:P29"/>
+    <mergeCell ref="E6:P6"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="E26:P26"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="E16:P16"/>
+    <mergeCell ref="C2:P2"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E22:P22"/>
+    <mergeCell ref="E18:P18"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E12:P12"/>
+    <mergeCell ref="E24:P24"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E8:P8"/>
+    <mergeCell ref="E14:P14"/>
+    <mergeCell ref="B12:D12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F766E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1024,336 +2276,336 @@
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— SETUP</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Fill in the amber cells — do not edit white formula cells</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="4" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>01  —  PRACTICE INFORMATION</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Practice Name</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>[Your Practice Name]</t>
         </is>
       </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="9" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="19" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Tagline / Descriptor</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>[e.g., Bookkeeping for service businesses]</t>
         </is>
       </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="9" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="19" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Owner / Bookkeeper Name</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>[Your Name]</t>
         </is>
       </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="19" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Email Address</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>[your@email.com]</t>
         </is>
       </c>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="9" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="19" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>[Your Phone]</t>
         </is>
       </c>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="9" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="19" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Website / Portal URL</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>[https://yoursite.com]</t>
         </is>
       </c>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="9" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="19" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Bookkeeping Software Used</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>[QuickBooks Online / Xero / Wave / Other]</t>
         </is>
       </c>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="9" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="19" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Currency Symbol</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="9" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="19" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Monthly Close Day (of following month)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="9" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="19" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Fiscal Year End Month</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>December</t>
         </is>
       </c>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="9" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="19" t="n"/>
     </row>
     <row r="19" ht="4" customHeight="1"/>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>02  —  SERVICE TIERS</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="17" t="n"/>
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="17" t="n"/>
+      <c r="P20" s="17" t="n"/>
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Tier Name</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>Monthly Transactions</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>Accounts</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>Monthly Fee (€)</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>Hourly Rate (€)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Essentials</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="24" t="n">
         <v>650</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F23" s="24" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="27" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="23" t="n">
         <v>600</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="24" t="n">
         <v>2200</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="24" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1386,623 +2638,320 @@
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
+  <dataValidations count="10">
+    <dataValidation sqref="F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Required Field" error="Please enter a value" type="textLength" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:R27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="1.5" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="10" customHeight="1"/>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>— INSTRUCTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>How to use every sheet in this dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
-    </row>
-    <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="36" customHeight="1">
-      <c r="B6" s="50" t="inlineStr">
-        <is>
-          <t>01 — SETUP</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="n"/>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="51" t="inlineStr">
-        <is>
-          <t>Fill in the amber cells only. White cells contain formulas that reference Setup data — do not edit them. Changes to Practice Name and pricing cascade to the Pricing Calculator.</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="4" customHeight="1"/>
-    <row r="8" ht="36" customHeight="1">
-      <c r="B8" s="50" t="inlineStr">
-        <is>
-          <t>02 — CLIENT CRM</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="51" t="inlineStr">
-        <is>
-          <t>Add one row per client. The Status column (Active/Churned/On Hold) drives the Dashboard KPIs. Use the Package dropdown to match your service tiers. The MRR formula at the bottom sums only Active clients.</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="4" customHeight="1"/>
-    <row r="10" ht="36" customHeight="1">
-      <c r="B10" s="50" t="inlineStr">
-        <is>
-          <t>03 — LEAD PIPELINE</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="n"/>
-      <c r="E10" s="51" t="inlineStr">
-        <is>
-          <t>Add a row for each prospect. The Pipeline Value at the bottom sums all leads not marked Closed Lost. Move Stage through the dropdown — from New Inquiry to Closed Won.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="4" customHeight="1"/>
-    <row r="12" ht="36" customHeight="1">
-      <c r="B12" s="50" t="inlineStr">
-        <is>
-          <t>04 — PRICING CALCULATOR</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="51" t="inlineStr">
-        <is>
-          <t>Enter the prospect's details in the amber cells. The calculator produces a recommended monthly fee and cleanup estimate. Use it during diagnostic calls.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="4" customHeight="1"/>
-    <row r="14" ht="36" customHeight="1">
-      <c r="B14" s="50" t="inlineStr">
-        <is>
-          <t>05 — MONTHLY CLOSE</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="51" t="inlineStr">
-        <is>
-          <t>Add one row per client per period (e.g., "2026-07"). Use the Status and checkbox dropdowns (Yes/No) to track progress. Conditional formatting turns cells teal when complete.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="4" customHeight="1"/>
-    <row r="16" ht="36" customHeight="1">
-      <c r="B16" s="50" t="inlineStr">
-        <is>
-          <t>06 — INVOICE TRACKER</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="51" t="inlineStr">
-        <is>
-          <t>Add one row per invoice. Status drives the Outstanding balance formula at the bottom. Mark Paid invoices with the payment date. Overdue rows turn red automatically.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="4" customHeight="1"/>
-    <row r="18" ht="36" customHeight="1">
-      <c r="B18" s="50" t="inlineStr">
-        <is>
-          <t>07 — TAX DOCUMENTS</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="29" t="n"/>
-      <c r="E18" s="51" t="inlineStr">
-        <is>
-          <t>Use this sheet at year-end. One row per client per fiscal year. Track document collection across all categories. Mark items N/A if they do not apply to that client.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="4" customHeight="1"/>
-    <row r="20" ht="36" customHeight="1">
-      <c r="B20" s="50" t="inlineStr">
-        <is>
-          <t>08 — CAPACITY PLANNER</t>
-        </is>
-      </c>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="51" t="inlineStr">
-        <is>
-          <t>Enter your weekly available hours and admin time. Add one row per client with their average monthly hours. The sheet shows whether you are over or under capacity.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="4" customHeight="1"/>
-    <row r="22" ht="36" customHeight="1">
-      <c r="B22" s="50" t="inlineStr">
-        <is>
-          <t>09 — DASHBOARD</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="51" t="inlineStr">
-        <is>
-          <t>This sheet auto-populates from all other sheets. Do not enter data here directly. KPI cards show active clients, MRR, pipeline value, and close status in real time.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="4" customHeight="1"/>
-    <row r="24" ht="36" customHeight="1">
-      <c r="B24" s="50" t="inlineStr">
-        <is>
-          <t>10 — INSTRUCTIONS</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="51" t="inlineStr">
-        <is>
-          <t>This sheet. Reference it anytime you are unsure about a feature.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="4" customHeight="1"/>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="52" t="inlineStr">
-        <is>
-          <t>TIP: Only edit cells with amber background. Never edit cells with teal or dark backgrounds — those contain formulas or are read-only display areas.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E20:P20"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E10:P10"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E6:P6"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A4:R4"/>
-    <mergeCell ref="E16:P16"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="E22:P22"/>
-    <mergeCell ref="E18:P18"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E12:P12"/>
-    <mergeCell ref="E24:P24"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E8:P8"/>
-    <mergeCell ref="E14:P14"/>
-    <mergeCell ref="B27:P27"/>
-    <mergeCell ref="B12:D12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— CLIENT CRM</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Master record for all active and former clients</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Client Name</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Entity Type</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Monthly Fee (€)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Close Day</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Primary Contact</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Tax Preparer</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Service Package</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Harbor Design LLC</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>LLC</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>QuickBooks Online</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="24" t="n">
         <v>850</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Alex Morgan</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>alex@example.com</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>[Tax Preparer]</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr"/>
+      <c r="M7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>S-Corp</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Xero</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>Jamie Chen</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>jamie@example.com</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>[Tax Preparer]</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="26" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>[Client Name]</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>[Entity]</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>[Software]</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>[Contact]</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>[Email]</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>[Tax Preparer]</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="K9" s="23" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t>Essentials</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr"/>
+      <c r="M9" s="23" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY RECURRING REVENUE</t>
         </is>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="29">
         <f>SUMIF(C7:C200,"Active",F7:F200)</f>
         <v/>
       </c>
@@ -2032,15 +2981,16 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2055,188 +3005,188 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— LEAD PIPELINE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Track every prospect from first contact to closed deal</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Lead / Contact Name</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Est. Monthly Fee (€)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Cleanup Est. (€)</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Next Action</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Next Action Date</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Jamie Chen</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Diagnostic Scheduled</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Referral</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="24" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Run diagnostic</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>jamie@example.com</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr"/>
+      <c r="K7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>[Lead Name]</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>[Company]</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>New Inquiry</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>[Source]</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>[Action]</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr"/>
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>[Email]</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr"/>
+      <c r="K8" s="26" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>TOTAL PIPELINE VALUE (MONTHLY)</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="31">
         <f>SUMIF(D7:D200,"&lt;&gt;Closed Lost",F7:F200)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>OPEN LEAD COUNT</t>
         </is>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="33">
         <f>COUNTIF(D7:D200,"&lt;&gt;Closed Lost")-COUNTIF(D7:D200,"Closed Won")</f>
         <v/>
       </c>
@@ -2267,15 +3217,16 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D97706"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2285,344 +3236,344 @@
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— PRICING CALCULATOR</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Calculate client fees based on scope — fill amber cells</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="4" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>01  —  CLIENT INPUTS</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Monthly Bank Transactions</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="24" t="n">
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="9" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="19" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Number of Bank Accounts</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="24" t="n">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="9" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="19" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Number of Credit Cards</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="24" t="n">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="9" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="19" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Has Payroll?  (1=Yes / 0=No)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="24" t="n">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="9" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="19" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Has Sales Tax / VAT?  (1=Yes / 0=No)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="24" t="n">
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="9" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="19" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Has Multi-Entity / Class Tracking?  (1=Yes / 0=No)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="24" t="n">
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="9" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="19" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Has Foreign Currency?  (1=Yes / 0=No)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="24" t="n">
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="19" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Cleanup Months Needed</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="24" t="n">
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="19" t="n"/>
     </row>
     <row r="17" ht="4" customHeight="1"/>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>02  —  CALCULATED FEES</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="17" t="n"/>
+      <c r="P18" s="17" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Base Monthly Fee</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="25">
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="35">
         <f>IF(H9&lt;=100,650,IF(H9&lt;=300,1200,2200))</f>
         <v/>
       </c>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="19" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Payroll Add-On</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="25">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="35">
         <f>IF(H12=1,150,0)</f>
         <v/>
       </c>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="19" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Sales Tax / VAT Add-On</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="25">
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="35">
         <f>IF(H13=1,100,0)</f>
         <v/>
       </c>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="19" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Multi-Entity Add-On</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="25">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="35">
         <f>IF(H14=1,300,0)</f>
         <v/>
       </c>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="19" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Foreign Currency Add-On</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="25">
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="35">
         <f>IF(H15=1,200,0)</f>
         <v/>
       </c>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="9" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="19" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Cleanup Project Estimate</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="25">
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="35">
         <f>H16*400</f>
         <v/>
       </c>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="9" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="19" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>RECOMMENDED MONTHLY FEE</t>
         </is>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="37">
         <f>SUM(H20:H25)-H25</f>
         <v/>
       </c>
-      <c r="I26" s="28" t="n"/>
-      <c r="J26" s="29" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="39" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>CLEANUP PROJECT ESTIMATE (one-time)</t>
         </is>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="41">
         <f>H26</f>
         <v/>
       </c>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="33" t="n"/>
+      <c r="I27" s="42" t="n"/>
+      <c r="J27" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -2666,17 +3617,18 @@
     <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:R9"/>
+  <dimension ref="A2:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
@@ -2686,254 +3638,266 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— MONTHLY CLOSE TRACKER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Track close status for every client each period</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Bank Rec.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Card Rec.</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Questions Sent</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Questions Answered</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Reports Delivered</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Review Notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Harbor Design LLC</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>[OWNER]</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr"/>
+      <c r="L7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>[OWNER]</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="L8" s="26" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>[Client Name]</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>[OWNER]</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr"/>
+      <c r="K9" s="23" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>CLOSE PROGRESS</t>
+        </is>
+      </c>
+      <c r="D11" s="45">
+        <f>IFERROR(COUNTIF(D7:D9,"Delivered")/COUNTA(C7:C9),0)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B3:P3"/>
     <mergeCell ref="C2:P2"/>
-    <mergeCell ref="B3:P3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:R4"/>
   </mergeCells>
@@ -2953,6 +3917,18 @@
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="4">
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" dxfId="5">
+      <formula>0.5</formula>
+      <formula>0.8</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="lessThan" dxfId="6">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="D7:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Questions Pending,Under Review,Delivered,On Hold"</formula1>
@@ -2962,15 +3938,16 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2978,252 +3955,252 @@
     <col width="1.5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— INVOICE TRACKER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Track all invoices, payment status, and outstanding balances</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Invoice #</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Issue Date</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Amount (€)</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Paid Date</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Service Period</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>INV-001</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Harbor Design LLC</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="24" t="n">
         <v>850</v>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>Bank Transfer</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr"/>
+      <c r="K7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>INV-002</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>Bank Transfer</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr"/>
+      <c r="K8" s="26" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>INV-003</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>[Client Name]</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>Draft</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr"/>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr"/>
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr"/>
+      <c r="J9" s="23" t="inlineStr"/>
+      <c r="K9" s="23" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>TOTAL INVOICED</t>
         </is>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="31">
         <f>SUMIF(G7:G500,"&lt;&gt;Void",F7:F500)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>TOTAL PAID</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="31">
         <f>SUMIF(G7:G500,"Paid",F7:F500)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>TOTAL OUTSTANDING</t>
         </is>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="46">
         <f>SUMIF(G7:G500,"Sent",F7:F500)+SUMIF(G7:G500,"Overdue",F7:F500)</f>
         <v/>
       </c>
@@ -3252,15 +4229,16 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3268,220 +4246,220 @@
     <col width="1.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— TAX DOCUMENTS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Track year-end document collection status per client</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Fiscal Year</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Income Docs</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>Bank Stmts</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>Assets/Debt</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Tax/Compliance</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Owner Activity</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>Package Delivered</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>Tax Preparer</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Harbor Design LLC</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>[Tax Preparer]</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr"/>
+      <c r="M7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>[Tax Preparer]</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3504,257 +4482,258 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1"/>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>— CAPACITY PLANNER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Plan your available hours vs. committed client time</t>
         </is>
       </c>
     </row>
     <row r="4" ht="3" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="4" customHeight="1"/>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>01  —  WEEKLY CAPACITY INPUTS</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Total available hours per week</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="24" t="n">
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="9" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="19" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Admin / sales hours per week</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="24" t="n">
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="9" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="19" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Buffer / training hours per week</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="24" t="n">
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="19" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Billable hours available per week</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="35">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="47">
         <f>G9-G10-G11</f>
         <v/>
       </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="9" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="19" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1"/>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>02  —  CLIENT TIME COMMITMENTS</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="17" t="n"/>
+      <c r="L14" s="17" t="n"/>
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="17" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Avg Hours/Month</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>Hours/Week</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Harbor Design LLC</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="48">
         <f>D17/4</f>
         <v/>
       </c>
-      <c r="F17" s="13" t="inlineStr"/>
+      <c r="F17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Oak &amp; Pine Co.</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Advanced</t>
         </is>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="E18" s="37">
+      <c r="E18" s="49">
         <f>D18/4</f>
         <v/>
       </c>
-      <c r="F18" s="16" t="inlineStr"/>
+      <c r="F18" s="26" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>[Client Name]</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Essentials</t>
         </is>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="48">
         <f>D19/4</f>
         <v/>
       </c>
-      <c r="F19" s="13" t="inlineStr"/>
+      <c r="F19" s="23" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>TOTAL COMMITTED HOURS / WEEK</t>
         </is>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="50">
         <f>SUM(E17:E20)</f>
         <v/>
       </c>
@@ -3778,540 +4757,6 @@
     <mergeCell ref="A4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F172A"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:T23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14" customHeight="1"/>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>BOOKKEEPER PRACTICE DASHBOARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="40" t="inlineStr">
-        <is>
-          <t>v2.0   ·   Consulting Edition   ·   Live data from all sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="4" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
-    </row>
-    <row r="5" ht="12" customHeight="1"/>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="41" t="inlineStr">
-        <is>
-          <t>ACTIVE CLIENTS</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="41" t="inlineStr">
-        <is>
-          <t>MONTHLY RECURRING REVENUE</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>OPEN PIPELINE VALUE</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="41" t="inlineStr">
-        <is>
-          <t>ACTIVE LEADS</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="41" t="inlineStr">
-        <is>
-          <t>TOTAL INVOICED (YTD)</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="41" t="inlineStr">
-        <is>
-          <t>CLOSES IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="n"/>
-      <c r="R6" s="9" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="42">
-        <f>COUNTIF('Client CRM'!C:C,"Active")</f>
-        <v/>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="43">
-        <f>SUMIF('Client CRM'!C:C,"Active",'Client CRM'!F:F)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="44">
-        <f>SUMIF('Lead Pipeline'!D:D,"&lt;&gt;Closed Lost",'Lead Pipeline'!F:F)</f>
-        <v/>
-      </c>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="45">
-        <f>COUNTIF('Lead Pipeline'!D:D,"&lt;&gt;Closed Lost")-COUNTIF('Lead Pipeline'!D:D,"Closed Won")</f>
-        <v/>
-      </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="43">
-        <f>SUMIF('Invoice Tracker'!G:G,"&lt;&gt;Void",'Invoice Tracker'!F:F)</f>
-        <v/>
-      </c>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="42">
-        <f>COUNTIF('Monthly Close'!D:D,"In Progress")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8" t="n"/>
-      <c r="R7" s="9" t="n"/>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
-        <is>
-          <t>from Client CRM</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="46" t="inlineStr">
-        <is>
-          <t>total active fees</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="46" t="inlineStr">
-        <is>
-          <t>est. monthly from leads</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="46" t="inlineStr">
-        <is>
-          <t>in pipeline</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="46" t="inlineStr">
-        <is>
-          <t>all non-void invoices</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="46" t="inlineStr">
-        <is>
-          <t>this month</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="n"/>
-      <c r="R8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="4" customHeight="1">
-      <c r="A9" s="47" t="n"/>
-      <c r="B9" s="47" t="n"/>
-      <c r="C9" s="47" t="n"/>
-      <c r="D9" s="47" t="n"/>
-      <c r="E9" s="47" t="n"/>
-      <c r="F9" s="47" t="n"/>
-      <c r="G9" s="48" t="n"/>
-      <c r="H9" s="48" t="n"/>
-      <c r="I9" s="48" t="n"/>
-      <c r="J9" s="48" t="n"/>
-      <c r="K9" s="48" t="n"/>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="47" t="n"/>
-      <c r="N9" s="47" t="n"/>
-      <c r="O9" s="47" t="n"/>
-      <c r="P9" s="47" t="n"/>
-      <c r="Q9" s="47" t="n"/>
-      <c r="R9" s="47" t="n"/>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
-        <is>
-          <t>01 — ACTIVE CLIENT SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Fee (€)</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>Close Day</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="12">
-        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+0),"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="15">
-        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+1),"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!B:B,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!L:L,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!F:F,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!G:G,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!H:H,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="12">
-        <f>IFERROR(INDEX('Client CRM'!E:E,MATCH("Active",'Client CRM'!C:C,0)+2),"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="49" t="inlineStr">
-        <is>
-          <t>02 — MONTHLY CLOSE STATUS — CURRENT PERIOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Bank Rec</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>Reports Delivered</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!C:C,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!D:D,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!F:F,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!J:J,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!K:K,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!E:E,1+1),"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!C:C,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!D:D,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!F:F,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!J:J,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!K:K,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="15">
-        <f>IFERROR(INDEX('Monthly Close'!E:E,2+1),"")</f>
-        <v/>
-      </c>
-      <c r="L22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!C:C,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!D:D,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!F:F,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!J:J,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!K:K,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="12">
-        <f>IFERROR(INDEX('Monthly Close'!E:E,3+1),"")</f>
-        <v/>
-      </c>
-      <c r="L23" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="E21:F21"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>